--- a/Reports/module_summary.xlsx
+++ b/Reports/module_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,21 +493,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aman Kumar</t>
+          <t>Akeel Khan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ak8102347910@gmail.com</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>akeelkhan3499@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>33.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -518,314 +518,316 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mohammad Akeel</t>
+          <t>Akash Kumar Yadav</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>akeelkhan3499@gmail.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>akyadav5769@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>88</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>75</v>
+      </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>82.22222222222221</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Akash Kumar Yadav</t>
+          <t>Alok</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>akyadav5769@gmail.com</t>
+          <t>alok_kumar@liet.in</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>75</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>82.22222222222221</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALOK </t>
+          <t xml:space="preserve">Aman Kumar </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>alok_kumar@liet.in</t>
+          <t>amankumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.666666666666667</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>80</v>
+      </c>
       <c r="F6" t="n">
-        <v>6.666666666666667</v>
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aman Kumar</t>
+          <t xml:space="preserve">Aman Singh </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>amankumarbtech23-27@liet.in</t>
+          <t>amans64788@gmail.com</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="D7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" t="n">
-        <v>80</v>
-      </c>
+        <v>87.5</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>53.33333333333334</v>
+        <v>87.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aman Singh</t>
+          <t>Aman singh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>amans64788@gmail.com</t>
+          <t>amansingh1btech23-27@liet.in</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>78.26086956521739</v>
+      </c>
+      <c r="D8" t="n">
+        <v>84.61538461538461</v>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>87.5</v>
+        <v>79.43262411347519</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aman Singh</t>
+          <t xml:space="preserve">Amrendra Ram Tripathi </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>amansingh1btech23-27@liet.in</t>
+          <t>amrendraramtripathibtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>78.26086956521739</v>
-      </c>
-      <c r="D9" t="n">
-        <v>84.61538461538461</v>
-      </c>
+        <v>93.33333333333333</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>79.43262411347519</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amrendra Ram Tripathi</t>
+          <t>Anshu Gupta</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>amrendraramtripathibtech23-27@liet.in</t>
+          <t>ansh.gup067@gmail.com</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>75.29411764705883</v>
+      </c>
+      <c r="D10" t="n">
+        <v>93.75</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>93.33333333333333</v>
+        <v>78.21782178217822</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anshu Gupta</t>
+          <t xml:space="preserve">Ansh Tyagi </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ansh.gup067@gmail.com</t>
+          <t>anshtyagi189@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.29411764705883</v>
+        <v>93.04347826086956</v>
       </c>
       <c r="D11" t="n">
-        <v>93.75</v>
+        <v>88.46153846153845</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>78.21782178217822</v>
+        <v>92.19858156028369</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ansh Tyagi</t>
+          <t>Anushka Garg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>anshtyagi189@gmail.com</t>
+          <t>anushkagargbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>93.04347826086956</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>88.46153846153845</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>81.25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>90</v>
+      </c>
       <c r="F12" t="n">
-        <v>92.19858156028369</v>
+        <v>88.1578947368421</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anushka Garg</t>
+          <t>Anurag Kumar Singh</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>anushkagargbtech23-27@liet.in</t>
+          <t>anusingh99361634@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
-      </c>
-      <c r="D13" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="E13" t="n">
-        <v>90</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>88.1578947368421</v>
+        <v>91</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anurag Kumar Singh</t>
+          <t>Ayush Pal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>anusingh99361634@gmail.com</t>
+          <t>ayushpalbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="D14" t="n">
+        <v>68.75</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>78.44827586206897</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ayush Pal</t>
+          <t>Ayush Saw</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ayushpalbtech23-27@liet.in</t>
+          <t>ayushsawbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="D15" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>76.92307692307693</v>
+      </c>
+      <c r="E15" t="n">
+        <v>85</v>
+      </c>
       <c r="F15" t="n">
-        <v>78.44827586206897</v>
+        <v>76.74418604651163</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -836,54 +838,54 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ayush Saw</t>
+          <t>Ayush Singh</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ayushsawbtech23-27@liet.in</t>
+          <t>ayushsingh50593@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>72.5</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>76.92307692307693</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F16" t="n">
-        <v>76.74418604651163</v>
+        <v>93.44262295081968</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ayush Singh</t>
+          <t>Chetan Goswami</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ayushsingh50593@gmail.com</t>
+          <t>chetangoswami2006@gmail.com</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>93.33333333333333</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="D17" t="n">
         <v>92.30769230769231</v>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>93.44262295081968</v>
+        <v>93.12977099236642</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -894,187 +896,189 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chetan gooswami</t>
+          <t>Deepanshu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chetangoswami2006@gmail.com</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
-        <v>93.75</v>
-      </c>
+          <t>deepanshu3btech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>96.52173913043478</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>93.75</v>
+        <v>96.52173913043478</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chetan Goswami</t>
+          <t>Devashish Dobhal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chetangoswamibtech23-27@liet.in</t>
+          <t>devashishdobhalbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>95.29411764705881</v>
+        <v>81.73913043478261</v>
       </c>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>62.5</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
-        <v>93.04347826086956</v>
+        <v>76.82119205298014</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deepanshu</t>
+          <t>Garima Singh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepanshu3btech23-27@liet.in</t>
+          <t>gsinghakca@gmail.com</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>96.52173913043478</v>
+        <v>77.33333333333333</v>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>90</v>
+      </c>
       <c r="F20" t="n">
-        <v>96.52173913043478</v>
+        <v>80</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Devashish Dobhal</t>
+          <t xml:space="preserve">Gunjan </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>devashishdobhalbtech23-27@liet.in</t>
+          <t>gunjanbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>81.73913043478261</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="D21" t="n">
-        <v>62.5</v>
+        <v>80.76923076923077</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>76.82119205298014</v>
+        <v>89.31297709923665</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Garima Singh</t>
+          <t xml:space="preserve">Gurmeet Singh </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gsinghakca@gmail.com</t>
+          <t>gurmeetsinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>77.33333333333333</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>90</v>
-      </c>
+        <v>67.05882352941175</v>
+      </c>
+      <c r="D22" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>70.29702970297029</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gunjan</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gunjanbtech23-27@liet.in</t>
+          <t>happybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>73.07692307692307</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F23" t="n">
-        <v>88.88888888888889</v>
+        <v>78.08219178082192</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunjan </t>
+          <t xml:space="preserve">Harshit Rai </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gunjanchaudhary@liet.in</t>
+          <t>harshitraibtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>96</v>
+        <v>91.30434782608695</v>
       </c>
       <c r="D24" t="n">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>90.2439024390244</v>
+        <v>90.83969465648855</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1085,270 +1089,272 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gurmeet Singh</t>
+          <t>Jai Vardhan Singh</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gurmeetsinghbtech23-27@liet.in</t>
+          <t>jaisingh1256301@gmail.com</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67.05882352941175</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>81.66666666666667</v>
+      </c>
+      <c r="D25" t="n">
+        <v>62.5</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>67.05882352941175</v>
+        <v>77.63157894736842</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t xml:space="preserve">Kanak Gupta </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>happybtech23-27@liet.in</t>
+          <t>kanak.gup1234@gmail.com</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>78</v>
+        <v>92.17391304347827</v>
       </c>
       <c r="D26" t="n">
-        <v>73.07692307692307</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="E26" t="n">
         <v>85</v>
       </c>
       <c r="F26" t="n">
-        <v>78.08219178082192</v>
+        <v>91.30434782608695</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Harshit Rai</t>
+          <t xml:space="preserve">Krishna Kumar Sah </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>harshitrai1822@gmail.com</t>
+          <t>ksah9189@gmail.com</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>91.30434782608695</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>90.83969465648855</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jagat Kumar</t>
+          <t>Ritik</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jagat.kumar@liet.in</t>
+          <t>kumarritik38269@gmail.com</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
+        <v>73.91304347826086</v>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>26.66666666666667</v>
+        <v>68.94409937888199</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jai</t>
+          <t>Kapil Yadav</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jaisingh1256301@gmail.com</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>ky205426@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>77.64705882352942</v>
+      </c>
       <c r="D29" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>65.38461538461539</v>
+      </c>
+      <c r="E29" t="n">
+        <v>70</v>
+      </c>
       <c r="F29" t="n">
-        <v>62.5</v>
+        <v>74.04580152671755</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jai Vardhan Singh</t>
+          <t xml:space="preserve">Manish Mishra </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jaivardhansinghbtech23-27@liet.in</t>
+          <t>manishjitendramishrabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>81.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>81.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kanak Gupta</t>
+          <t>Akeel khan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kanak.gup1234@gmail.com</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>92.17391304347827</v>
-      </c>
-      <c r="D31" t="n">
-        <v>92.30769230769231</v>
-      </c>
+          <t>mohammadakeelbtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="F31" t="n">
-        <v>91.30434782608695</v>
+        <v>35</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Krishna Kumar Sah</t>
+          <t>MOHIT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>krishnakumarsahbtech23-27@liet.in</t>
+          <t>mohitbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>45</v>
+        <v>83.47826086956522</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
+        <v>68.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>90</v>
+      </c>
       <c r="F32" t="n">
-        <v>46.42857142857143</v>
+        <v>82.78145695364239</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ritik</t>
+          <t xml:space="preserve">Mohit Kumar </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kumarritik38269@gmail.com</t>
+          <t>mohitkumar746185@gmail.com</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.91304347826086</v>
+        <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>46.15384615384615</v>
-      </c>
-      <c r="E33" t="n">
-        <v>70</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>68.94409937888199</v>
+        <v>96</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kapil Yadav</t>
+          <t xml:space="preserve">Mushroop </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ky205426@gmail.com</t>
+          <t>mushroopbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>77.64705882352942</v>
       </c>
       <c r="D34" t="n">
-        <v>65.38461538461539</v>
+        <v>73.07692307692307</v>
       </c>
       <c r="E34" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F34" t="n">
-        <v>74.04580152671755</v>
+        <v>76.33587786259542</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1359,179 +1365,183 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manish Mishra </t>
+          <t xml:space="preserve">Nikhil Sharma </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>manishjitendramishrabtech23-27@liet.in</t>
+          <t>nikhilsharmabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mushroop</t>
+          <t xml:space="preserve">Nilesh Sarkar </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mdmushroop@gmail.com</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>68</v>
-      </c>
-      <c r="D36" t="n">
-        <v>70</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>nileshsarkar430@email.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>90</v>
+      </c>
       <c r="F36" t="n">
-        <v>68.57142857142857</v>
+        <v>90</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Akeel khan</t>
+          <t xml:space="preserve">Nilesh Sarkar </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mohammadakeelbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>35</v>
-      </c>
+          <t>nileshsarkar430@gmail.com</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>75.65217391304347</v>
+      </c>
+      <c r="D37" t="n">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>78.01418439716312</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mohit</t>
+          <t xml:space="preserve">Nisha Gupta </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mohitbtech23-27@liet.in</t>
+          <t>nishaguptabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>83.47826086956522</v>
-      </c>
-      <c r="D38" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="E38" t="n">
-        <v>90</v>
-      </c>
+        <v>73.33333333333333</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>82.78145695364239</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mohit Kumar</t>
+          <t>PIYUSH SINGH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mohitkumar746185@gmail.com</t>
+          <t>piyushsingh1982004@gmail.com</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="D39" t="n">
-        <v>90</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>84.61538461538461</v>
+      </c>
+      <c r="E39" t="n">
+        <v>80</v>
+      </c>
       <c r="F39" t="n">
-        <v>96</v>
+        <v>68.49315068493151</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mushroop </t>
+          <t xml:space="preserve">Prateek Rai </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mushroopbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>prateekraibtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>92</v>
+      </c>
+      <c r="D40" t="n">
+        <v>81.25</v>
+      </c>
       <c r="E40" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F40" t="n">
-        <v>75</v>
+        <v>86.76470588235294</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mushroop</t>
+          <t>Prem Kumar Jha</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mushroopmd08@gmail.com</t>
+          <t>premkumarjhabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>81.66666666666667</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="D41" t="n">
+        <v>87.5</v>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>81.66666666666667</v>
+        <v>89.65517241379311</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1542,131 +1552,135 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nilesh Sarkar</t>
+          <t xml:space="preserve">Pushpendra Yadav </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nileshsarkar430@gmail.com</t>
+          <t>pushpendrayadav8434@gmail.com</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>75.65217391304347</v>
+        <v>76</v>
       </c>
       <c r="D42" t="n">
-        <v>88.46153846153845</v>
-      </c>
-      <c r="E42" t="n">
-        <v>90</v>
-      </c>
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>79.50310559006211</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nisha Gupta</t>
+          <t>Rahul Yadav</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nishaguptabtech23-27@liet.in</t>
+          <t>rahulyadavbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>84.44444444444444</v>
+      </c>
+      <c r="D43" t="n">
+        <v>75</v>
+      </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>73.33333333333333</v>
+        <v>83.01886792452831</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nikhil Sharma</t>
+          <t>Ritesh Kumar Singh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ns977440@gmail.com</t>
+          <t>riteshkumar07.com@gmail.com</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>80</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+        <v>93.33333333333333</v>
+      </c>
+      <c r="D44" t="n">
+        <v>87.5</v>
+      </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>80</v>
+        <v>92.10526315789474</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Piyush Singh</t>
+          <t xml:space="preserve">Rohit Kumar </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>piyushsinghbtech23-27@liet.in</t>
+          <t>rohitkumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>62</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="D45" t="n">
-        <v>84.61538461538461</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="E45" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n">
-        <v>68.49315068493151</v>
+        <v>56.48854961832062</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Prem Kumar Jha</t>
+          <t>Sakshi Chauhan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>premkumarjhabtech23-27@liet.in</t>
+          <t>sakshichauhanbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="D46" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>96.15384615384616</v>
+      </c>
+      <c r="E46" t="n">
+        <v>75</v>
+      </c>
       <c r="F46" t="n">
-        <v>89.65517241379311</v>
+        <v>83.85093167701864</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1677,23 +1691,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pushpendra Yadav</t>
+          <t xml:space="preserve">Sanskar </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pushpendrayadav8434@gmail.com</t>
+          <t>sanskarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>76</v>
-      </c>
-      <c r="D47" t="n">
-        <v>30.76923076923077</v>
-      </c>
+        <v>62.66666666666667</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>66.66666666666666</v>
+        <v>62.66666666666667</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1704,220 +1716,218 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rahul Yadav</t>
+          <t xml:space="preserve">Satyansh Rawat </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>rahulyadavbtech23-27@liet.in</t>
+          <t>satyanshrawatbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>84.44444444444444</v>
+        <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>83.01886792452831</v>
+        <v>77.86259541984732</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Prateek Rai</t>
+          <t xml:space="preserve">Shivam Chaudhary </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>raiprateek009@gmail.com</t>
+          <t>shivamchaudharybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="E49" t="n">
-        <v>65</v>
-      </c>
+        <v>76.92307692307693</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>86.76470588235294</v>
+        <v>79.36507936507937</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ritesh Kumar Singh</t>
+          <t xml:space="preserve">Shivangi Pandey </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>riteshkumar07.com@gmail.com</t>
+          <t>shivangipandeyabc@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>92.30769230769231</v>
+      </c>
+      <c r="E50" t="n">
+        <v>95</v>
+      </c>
       <c r="F50" t="n">
-        <v>92.10526315789474</v>
+        <v>95.58823529411765</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rohit Kumar</t>
+          <t>Sonu Kumar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>rohitkumarbtech23-27@liet.in</t>
+          <t>sonukumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>61.1764705882353</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="D51" t="n">
-        <v>46.15384615384615</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>56.48854961832062</v>
+        <v>48.35164835164835</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sakshi Chauhan</t>
+          <t xml:space="preserve">Sringani Singh </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>sakshichauhan5997@gmail.com</t>
+          <t>sringanisinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>82.60869565217391</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="D52" t="n">
-        <v>96.15384615384616</v>
+        <v>100</v>
       </c>
       <c r="E52" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F52" t="n">
-        <v>83.85093167701864</v>
+        <v>75.65217391304347</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Satyansh Rawat</t>
+          <t>Tarun kumar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>satyanshrawatbtech23-27@liet.in</t>
+          <t>tarunkumar1btech23-27@liet.in</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>80</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="D53" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>69.23076923076923</v>
+      </c>
+      <c r="E53" t="n">
+        <v>70</v>
+      </c>
       <c r="F53" t="n">
-        <v>77.86259541984732</v>
+        <v>80.15267175572519</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Shivam Chaudhary</t>
+          <t>Vaibhav Mishra</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>shivamchaudharybtech23-27@liet.in</t>
+          <t>vaibhavmishrabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D54" t="n">
-        <v>76.92307692307693</v>
+        <v>50</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>79.36507936507937</v>
+        <v>66</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Shivangi Pandey</t>
+          <t>Vibhu</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>shivangipandeyabc@gmail.com</t>
+          <t>vibhubtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>96.66666666666667</v>
-      </c>
-      <c r="D55" t="n">
-        <v>92.30769230769231</v>
-      </c>
-      <c r="E55" t="n">
-        <v>95</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>95.58823529411765</v>
+        <v>96</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1928,79 +1938,81 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sanskar</t>
+          <t>Vineet Kumar Roy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>solankisanskar01@gmail.com</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>62.66666666666667</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>vineet333roy@gmail.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>70</v>
+      </c>
+      <c r="E56" t="n">
+        <v>85</v>
+      </c>
       <c r="F56" t="n">
-        <v>62.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sonu Kumar</t>
+          <t xml:space="preserve">Vipul Pandey </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>sonukumar3570357@gmail.com</t>
+          <t>vipulpandeybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>72.72727272727273</v>
+        <v>91</v>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>76.92307692307693</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F57" t="n">
-        <v>48.35164835164835</v>
+        <v>88.35616438356165</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sringani Singh</t>
+          <t xml:space="preserve">Vishujeet Rathore </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sringanisinghbtech23-27@liet.in</t>
+          <t>vishujeetrathor@gmail.com</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>74.11764705882354</v>
+        <v>69</v>
       </c>
       <c r="D58" t="n">
-        <v>100</v>
+        <v>73.07692307692307</v>
       </c>
       <c r="E58" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F58" t="n">
-        <v>75.65217391304347</v>
+        <v>73.28767123287672</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2011,52 +2023,54 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tarun Kumar</t>
+          <t>Vivek Yadav</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>tarunpandit885@gmail.com</t>
+          <t>vivekyadavbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>85.88235294117646</v>
+        <v>81.73913043478261</v>
       </c>
       <c r="D59" t="n">
-        <v>69.23076923076923</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="E59" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F59" t="n">
-        <v>80.15267175572519</v>
+        <v>77.01863354037268</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vaibhav Mishra</t>
+          <t>Vishal Kumar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>vaibhavmishrabtech23-27@liet.in</t>
+          <t>vk9491015@gmail.com</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D60" t="n">
         <v>50</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>40</v>
+      </c>
       <c r="F60" t="n">
-        <v>66</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2067,287 +2081,52 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vineet Kumar Roy</t>
+          <t xml:space="preserve">Shreyanshi Yadav </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>vineet333roy@gmail.com</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="n">
-        <v>70</v>
-      </c>
+          <t>yadavshreyanshi772@gmail.com</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F61" t="n">
-        <v>80</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Vipul Pandey</t>
+          <t>Yash Bansal</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>vipulpandeybtech23-27@liet.in</t>
+          <t>yashbansal216@gmail.com</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>91</v>
-      </c>
-      <c r="D62" t="n">
-        <v>76.92307692307693</v>
-      </c>
-      <c r="E62" t="n">
-        <v>90</v>
-      </c>
+        <v>69.41176470588235</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>88.35616438356165</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Vishujeet Rathore</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>vishujeetrathor@gmail.com</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>77.33333333333333</v>
-      </c>
-      <c r="D63" t="n">
-        <v>73.07692307692307</v>
-      </c>
-      <c r="E63" t="n">
-        <v>95</v>
-      </c>
-      <c r="F63" t="n">
-        <v>79.33884297520662</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Vivek Yadav</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>vivekyadavbtech23-27@liet.in</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>81.73913043478261</v>
-      </c>
-      <c r="D64" t="n">
-        <v>65.38461538461539</v>
-      </c>
-      <c r="E64" t="n">
-        <v>65</v>
-      </c>
-      <c r="F64" t="n">
-        <v>77.01863354037268</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Vishal Kumar</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>vk9491015@gmail.com</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>76</v>
-      </c>
-      <c r="D65" t="n">
-        <v>50</v>
-      </c>
-      <c r="E65" t="n">
-        <v>40</v>
-      </c>
-      <c r="F65" t="n">
-        <v>67.64705882352942</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
           <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Shreyanshi Yadav</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>yadavshreyanshi022@gmail.com</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>55.00000000000001</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="n">
-        <v>75</v>
-      </c>
-      <c r="F66" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Yash Bansal</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>yashbansal216@gmail.com</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>69.41176470588235</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="n">
-        <v>69.41176470588235</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="n">
-        <v>44</v>
-      </c>
-      <c r="D68" t="n">
-        <v>75</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="n">
-        <v>56.09756097560976</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="n">
-        <v>44</v>
-      </c>
-      <c r="D69" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="n">
-        <v>60.97560975609756</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="n">
-        <v>96</v>
-      </c>
-      <c r="D70" t="n">
-        <v>75</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="n">
-        <v>87.80487804878049</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="n">
-        <v>96</v>
-      </c>
-      <c r="D71" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="n">
-        <v>92.6829268292683</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>A+</t>
         </is>
       </c>
     </row>
